--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488233_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488233_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1118</v>
+        <v>7.1708</v>
       </c>
       <c r="E2" t="n">
-        <v>5.264</v>
+        <v>5.5693</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8478</v>
+        <v>1.6016</v>
       </c>
       <c r="G2" t="n">
         <v>3.4007</v>
@@ -610,13 +610,13 @@
         <v>4.8175</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8257</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3109</v>
+        <v>-0.0056</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5149</v>
+        <v>-0.7611</v>
       </c>
       <c r="V2" t="n">
         <v>1.5722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3619</v>
+        <v>4.5687</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1673</v>
+        <v>3.4726</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1946</v>
+        <v>1.0961</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0331</v>
@@ -688,13 +688,13 @@
         <v>3.891</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4574</v>
+        <v>-0.2506</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1467</v>
+        <v>0.1586</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3107</v>
+        <v>-0.4091</v>
       </c>
       <c r="V3" t="n">
         <v>1.8877</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4962</v>
+        <v>2.1783</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2672</v>
+        <v>1.8755</v>
       </c>
       <c r="F4" t="n">
-        <v>0.229</v>
+        <v>0.3029</v>
       </c>
       <c r="G4" t="n">
         <v>0.0382</v>
@@ -766,13 +766,13 @@
         <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0492</v>
+        <v>-0.2686</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3793</v>
+        <v>-0.0124</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.33</v>
+        <v>-0.2562</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CASTILLO ORTEGA</t>
+          <t>J. LÓPEZ RUIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.45</v>
+        <v>1.8883</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1791</v>
+        <v>1.8883</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7291</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4994</v>
+        <v>1.8883</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5356</v>
+        <v>0.6441</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.035</v>
+        <v>1.2441</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3011</v>
+        <v>1.8883</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4717</v>
+        <v>0.6441</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8294</v>
+        <v>1.2441</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8005</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0639</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.8644</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8529</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.7057</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1062</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2137</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3199</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.5172</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LÓPEZ RUIZ</t>
+          <t>A. CASTILLO ORTEGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8883</v>
+        <v>1.654</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8883</v>
+        <v>2.3093</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.6553</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8883</v>
+        <v>-1.4994</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6441</v>
+        <v>0.5356</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2441</v>
+        <v>-2.035</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8883</v>
+        <v>1.3011</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6441</v>
+        <v>0.4717</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2441</v>
+        <v>0.8294</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-2.8005</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.0639</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-2.8644</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.7057</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.9022</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.3439</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-1.246</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.5172</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9845</v>
+        <v>0.5435</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6559</v>
+        <v>-1.0476</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6403</v>
+        <v>1.5911</v>
       </c>
       <c r="G7" t="n">
         <v>0.6664</v>
@@ -1000,13 +1000,13 @@
         <v>1.4823</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0766</v>
+        <v>-0.3644</v>
       </c>
       <c r="T7" t="n">
-        <v>0.434</v>
+        <v>0.0423</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3574</v>
+        <v>-0.4066</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3144</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1705</v>
+        <v>0.3177</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7341</v>
+        <v>-0.6361</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9045</v>
+        <v>0.9538</v>
       </c>
       <c r="G8" t="n">
         <v>0.2135</v>
@@ -1078,13 +1078,13 @@
         <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7842</v>
+        <v>-0.637</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1641</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.62</v>
+        <v>-0.5708</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3749</v>
+        <v>-1.9591</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7688</v>
+        <v>-1.2792</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.606</v>
+        <v>-0.6798999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>0.9465</v>
@@ -1234,13 +1234,13 @@
         <v>3.1499</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5802</v>
+        <v>-0.1645</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4924</v>
+        <v>-0.0028</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0878</v>
+        <v>-0.1617</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2589</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4234</v>
+        <v>-4.3823</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8316</v>
+        <v>-4.0367</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5918</v>
+        <v>-0.3456</v>
       </c>
       <c r="G11" t="n">
         <v>-3.0317</v>
@@ -1312,13 +1312,13 @@
         <v>4.8175</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.2446</v>
+        <v>-1.2034</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9637</v>
+        <v>-0.1688</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.2809</v>
+        <v>-1.0346</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2589</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.786</v>
+        <v>-5.554</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.9927</v>
+        <v>-3.7854</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7933</v>
+        <v>-1.7686</v>
       </c>
       <c r="G12" t="n">
         <v>-0.916</v>
@@ -1390,13 +1390,13 @@
         <v>2.7793</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1289</v>
+        <v>-0.8969</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4166</v>
+        <v>-0.2092</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7123</v>
+        <v>-0.6877</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8883</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.838900000000001</v>
+        <v>6.385900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>3.791000000000001</v>
+        <v>4.3382</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0477</v>
+        <v>2.047800000000001</v>
       </c>
       <c r="G13" t="n">
         <v>1.022800000000001</v>
@@ -1444,7 +1444,7 @@
         <v>16.8647</v>
       </c>
       <c r="K13" t="n">
-        <v>9.531299999999998</v>
+        <v>9.531300000000002</v>
       </c>
       <c r="L13" t="n">
         <v>7.3336</v>
@@ -1468,13 +1468,13 @@
         <v>28.7194</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.317299999999999</v>
+        <v>-5.770099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5221</v>
+        <v>0.02509999999999996</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.795000000000001</v>
+        <v>-5.7949</v>
       </c>
       <c r="V13" t="n">
         <v>0.9421000000000008</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0853</v>
+        <v>5.4621</v>
       </c>
       <c r="E14" t="n">
         <v>4.2931</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7922</v>
+        <v>1.169</v>
       </c>
       <c r="G14" t="n">
         <v>8.6168</v>
@@ -1546,13 +1546,13 @@
         <v>3.3352</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4887</v>
+        <v>0.8655</v>
       </c>
       <c r="T14" t="n">
         <v>0.725</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2363</v>
+        <v>0.1405</v>
       </c>
       <c r="V14" t="n">
         <v>-0.3144</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0298</v>
+        <v>3.8699</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5631</v>
+        <v>2.3466</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4667</v>
+        <v>1.5234</v>
       </c>
       <c r="G15" t="n">
         <v>1.5195</v>
@@ -1624,13 +1624,13 @@
         <v>2.594</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2308</v>
+        <v>0.6093</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3283</v>
+        <v>0.4551</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0975</v>
+        <v>0.1542</v>
       </c>
       <c r="V15" t="n">
         <v>0.6294</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>R. ROMERO NARANJO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.935</v>
+        <v>2.1722</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6469</v>
+        <v>1.6984</v>
       </c>
       <c r="F16" t="n">
-        <v>0.288</v>
+        <v>0.4738</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.885</v>
+        <v>1.7205</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6945</v>
+        <v>1.0463</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1905</v>
+        <v>0.6742</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3688</v>
+        <v>2.8691</v>
       </c>
       <c r="K16" t="n">
-        <v>0.09859999999999999</v>
+        <v>2.0183</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2702</v>
+        <v>0.8508</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2538</v>
+        <v>-1.1485</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7931</v>
+        <v>-0.972</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4607</v>
+        <v>-0.1766</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9264</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.3352</v>
+        <v>-1.8529</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4087</v>
+        <v>1.297</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2282</v>
+        <v>0.0631</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4661</v>
+        <v>0.3678</v>
       </c>
       <c r="U16" t="n">
-        <v>0.762</v>
+        <v>-0.3047</v>
       </c>
       <c r="V16" t="n">
-        <v>2.5183</v>
+        <v>0.9444</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1471</v>
+        <v>0.3144</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6289</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. ROMERO NARANJO</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4289</v>
+        <v>0.9786</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2088</v>
+        <v>0.9614</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2201</v>
+        <v>0.0172</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7205</v>
+        <v>-1.885</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0463</v>
+        <v>-1.6945</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6742</v>
+        <v>-0.1905</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8691</v>
+        <v>0.3688</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0183</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8508</v>
+        <v>0.2702</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1485</v>
+        <v>-2.2538</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.972</v>
+        <v>-1.7931</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1766</v>
+        <v>-0.4607</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.8529</v>
+        <v>-3.3352</v>
       </c>
       <c r="R17" t="n">
-        <v>1.297</v>
+        <v>2.4087</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6802</v>
+        <v>1.2718</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1219</v>
+        <v>0.7806</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5584</v>
+        <v>0.4912</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9444</v>
+        <v>2.5183</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3144</v>
+        <v>3.1471</v>
       </c>
       <c r="X17" t="n">
-        <v>0.63</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1732</v>
+        <v>0.55</v>
       </c>
       <c r="E18" t="n">
         <v>0.7107</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5375</v>
+        <v>-0.1607</v>
       </c>
       <c r="G18" t="n">
         <v>1.0739</v>
@@ -1858,13 +1858,13 @@
         <v>3.1499</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5434</v>
+        <v>0.9202</v>
       </c>
       <c r="T18" t="n">
         <v>0.7796999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2363</v>
+        <v>0.1405</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2589</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>R. FREIRE DELTIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1433</v>
+        <v>-2.2507</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6049</v>
+        <v>0.1349</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4616</v>
+        <v>-2.3856</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5663</v>
+        <v>-0.8141</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7799</v>
+        <v>-2.1042</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7863</v>
+        <v>1.2901</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5188</v>
+        <v>1.4021</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1456</v>
+        <v>-0.6099</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3732</v>
+        <v>2.012</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0851</v>
+        <v>-2.2161</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9255</v>
+        <v>-1.4943</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1596</v>
+        <v>-0.7219</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0382</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.8175</v>
+        <v>-1.297</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7793</v>
+        <v>0.9264</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7755</v>
+        <v>0.1928</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6937</v>
+        <v>0.0299</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0818</v>
+        <v>0.1629</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. FREIRE DELTIO</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6671</v>
+        <v>-2.6488</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2568</v>
+        <v>-1.8959</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4103</v>
+        <v>-0.7529</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8141</v>
+        <v>-2.1998</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1042</v>
+        <v>-0.968</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2901</v>
+        <v>-1.2318</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4021</v>
+        <v>-0.4655</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6099</v>
+        <v>-0.6314</v>
       </c>
       <c r="L20" t="n">
-        <v>2.012</v>
+        <v>0.1659</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2161</v>
+        <v>-1.7343</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4943</v>
+        <v>-0.3366</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7219</v>
+        <v>-1.3977</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3706</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.297</v>
+        <v>-1.8529</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2236</v>
+        <v>0.6065</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3619</v>
+        <v>0.4225</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1383</v>
+        <v>0.184</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1631</v>
+        <v>-2.7481</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3855</v>
+        <v>-3.1925</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7776</v>
+        <v>0.4444</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1998</v>
+        <v>-1.5663</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.968</v>
+        <v>-0.7799</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2318</v>
+        <v>-0.7863</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4655</v>
+        <v>0.5188</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6314</v>
+        <v>0.1456</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1659</v>
+        <v>0.3732</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7343</v>
+        <v>-2.0851</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3366</v>
+        <v>-0.9255</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3977</v>
+        <v>-1.1596</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7411</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8529</v>
+        <v>-4.8175</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1117</v>
+        <v>2.7793</v>
       </c>
       <c r="S21" t="n">
-        <v>0.09229999999999999</v>
+        <v>1.1708</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.06710000000000001</v>
+        <v>1.1061</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1594</v>
+        <v>0.0646</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3144</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0855</v>
+        <v>-4.306</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9284</v>
+        <v>-2.1243</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1571</v>
+        <v>-2.1817</v>
       </c>
       <c r="G22" t="n">
         <v>-4.1707</v>
@@ -2170,13 +2170,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7882</v>
+        <v>0.5677</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6616</v>
+        <v>0.4657</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1266</v>
+        <v>0.102</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2589</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.4319</v>
+        <v>-6.2651</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2948</v>
+        <v>-4.9803</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.137</v>
+        <v>-1.2848</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3178</v>
@@ -2248,13 +2248,13 @@
         <v>0.3706</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5355</v>
+        <v>0.7023</v>
       </c>
       <c r="T23" t="n">
-        <v>1.348</v>
+        <v>0.6625</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1875</v>
+        <v>0.0398</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3144</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8387</v>
+        <v>-5.1859</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.047800000000001</v>
+        <v>-2.047900000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.7909</v>
+        <v>-3.1379</v>
       </c>
       <c r="G24" t="n">
         <v>-1.023000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>18.5287</v>
       </c>
       <c r="S24" t="n">
-        <v>6.3172</v>
+        <v>6.970000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>5.7949</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5220999999999999</v>
+        <v>1.175</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9421999999999999</v>
